--- a/characters.xlsx
+++ b/characters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\genshinpuzzle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC83CA6-9B37-4A8E-B046-7A2170F6E69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0027B14B-8852-4027-929D-A9D52365BFC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{2BC2DB2F-00CC-4274-8DBF-E2A0BD6D3186}"/>
+    <workbookView xWindow="38280" yWindow="-105" windowWidth="38640" windowHeight="21120" xr2:uid="{2BC2DB2F-00CC-4274-8DBF-E2A0BD6D3186}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="215">
   <si>
     <t>Aino</t>
   </si>
@@ -673,6 +673,15 @@
   <si>
     <t>temper</t>
   </si>
+  <si>
+    <t>Vesna</t>
+  </si>
+  <si>
+    <t>Vodyanitsa</t>
+  </si>
+  <si>
+    <t>September 23, 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -52708,7 +52717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82BBB357-DBD0-43D1-9851-C679B1E8E460}">
-  <dimension ref="A1:K127"/>
+  <dimension ref="A1:K129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -55367,6 +55376,46 @@
         <v>0</v>
       </c>
       <c r="G127" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>212</v>
+      </c>
+      <c r="B128" t="s">
+        <v>20</v>
+      </c>
+      <c r="C128" t="s">
+        <v>214</v>
+      </c>
+      <c r="E128">
+        <v>5</v>
+      </c>
+      <c r="F128" t="b">
+        <v>0</v>
+      </c>
+      <c r="G128" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>213</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1</v>
+      </c>
+      <c r="C129" t="s">
+        <v>214</v>
+      </c>
+      <c r="E129">
+        <v>5</v>
+      </c>
+      <c r="F129" t="b">
+        <v>0</v>
+      </c>
+      <c r="G129" t="b">
         <v>0</v>
       </c>
     </row>
